--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:24</t>
+          <t>2026-09-03 00:52:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:26</t>
+          <t>2026-09-03 00:52:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:27</t>
+          <t>2026-09-03 00:52:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:28</t>
+          <t>2026-09-03 00:52:43</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:39</t>
+          <t>2026-09-03 01:12:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:41</t>
+          <t>2026-09-03 01:12:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:42</t>
+          <t>2026-09-03 01:12:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:43</t>
+          <t>2026-09-03 01:12:57</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.27%1,794,000</t>
+          <t>8.51%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.27%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.02%1,391,225</t>
+          <t>6.84%1,391,225</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>6.84%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.08%736,000</t>
+          <t>6.34%736,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.34%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%721</t>
+          <t>-1.25%712</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.26%3,771,000</t>
+          <t>5.33%3,771,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.57%469.5</t>
+          <t>-4.9%446.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>469.5</v>
+        <v>446.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.18%5,709,000</t>
+          <t>5.06%5,709,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13865</v>
+        <v>13450</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.90%183,000</t>
+          <t>4.89%183,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.83%254,000</t>
+          <t>3.61%254,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,25 +931,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5445</v>
+        <v>2015</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.32%315,000</t>
+          <t>3.32%830,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>315000</v>
+        <v>830000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.36%1445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1445</v>
+        <v>5290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.30%1,180,000</t>
+          <t>3.31%315,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1180000</v>
+        <v>315000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,34 +1053,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>-2.77%1405</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1975</v>
+        <v>1405</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.17%830,000</t>
+          <t>3.29%1,180,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>830000</v>
+        <v>1180000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5290</v>
+        <v>5045</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.14%307,000</t>
+          <t>3.08%307,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-4.7%912</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>507</v>
+        <v>912</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.09%3,158,000</t>
+          <t>3.01%1,660,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3158000</v>
+        <v>1660000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.1%957</t>
+          <t>-8.48%464</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-8.48%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>957</v>
+        <v>464</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.05%1,650,000</t>
+          <t>2.91%3,158,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1650000</v>
+        <v>3158000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.57%621,000</t>
+          <t>2.58%621,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:53</t>
+          <t>2026-09-03 21:25:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.39%374,000</t>
+          <t>2.45%374,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.72%967</t>
+          <t>-4.14%927</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.06%1,100,000</t>
+          <t>2.02%1,100,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+4.83%315</t>
+          <t>-2.6%674</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>315</v>
+        <v>674</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.98%3,258,000</t>
+          <t>1.96%1,466,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3258000</v>
+        <v>1466000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.67%692</t>
+          <t>-5.08%299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>692</v>
+        <v>299</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.96%1,466,000</t>
+          <t>1.93%3,258,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1466000</v>
+        <v>3258000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.07%757</t>
+          <t>-1.98%742</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-1.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.69%1,158,000</t>
+          <t>1.71%1,158,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.44%542</t>
+          <t>-3.14%525</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.44%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.63%1,553,000</t>
+          <t>1.62%1,553,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.65%155</t>
+          <t>+1.62%188.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>155</v>
+        <v>188.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.29%4,322,000</t>
+          <t>1.39%3,704,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4322000</v>
+        <v>3704000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.27%5,205,000</t>
+          <t>1.29%5,205,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.7%361.5</t>
+          <t>-2.9%150.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>361.5</v>
+        <v>150.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.24%1,773,000</t>
+          <t>1.29%4,322,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1773000</v>
+        <v>4322000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.27%183</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>183</v>
+        <v>17850</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.24%3,494,000</t>
+          <t>1.27%35,900</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3494000</v>
+        <v>35900</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>0%183</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>17725</v>
+        <v>183</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.23%35,900</t>
+          <t>1.27%3,494,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>35900</v>
+        <v>3494000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.92%185.5</t>
+          <t>-3.04%350.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>185.5</v>
+        <v>350.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.22%3,404,000</t>
+          <t>1.23%1,773,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3404000</v>
+        <v>1773000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.45%179</t>
+          <t>-1.68%176</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.20%3,481,000</t>
+          <t>1.22%3,481,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.19%178.5</t>
+          <t>-2.3%595</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>178.5</v>
+        <v>595</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.18%3,418,000</t>
+          <t>1.18%1,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3418000</v>
+        <v>1000000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.4%609</t>
+          <t>-3.08%173</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>609</v>
+        <v>173</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.18%1,000,000</t>
+          <t>1.17%3,418,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000000</v>
+        <v>3418000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:55</t>
+          <t>2026-09-03 21:25:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>-1.41%91.2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1410</v>
+        <v>91.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.17%428,000</t>
+          <t>1.17%6,445,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>428000</v>
+        <v>6445000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.84%92.5</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>92.5</v>
+        <v>1345</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.15%6,445,000</t>
+          <t>1.14%428,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6445000</v>
+        <v>428000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>-2.4%244.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>250.5</v>
+        <v>244.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.12%2,318,000</t>
+          <t>1.13%2,318,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.6%168.5</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>168.5</v>
+        <v>589</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.09%3,346,000</t>
+          <t>1.10%942,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>3346000</v>
+        <v>942000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>-3.56%162.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>589</v>
+        <v>162.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.07%942,000</t>
+          <t>1.08%3,346,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>942000</v>
+        <v>3346000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.02%121</t>
+          <t>-1.08%275</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.03%4,418,000</t>
+          <t>1.04%1,910,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>4418000</v>
+        <v>1910000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.11%278</t>
+          <t>-5.37%114.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>278</v>
+        <v>114.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.03%1,910,000</t>
+          <t>1.00%4,418,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1910000</v>
+        <v>4418000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.93%382,000</t>
+          <t>0.90%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.35%288</t>
+          <t>-2.6%411.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.35%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>288</v>
+        <v>411.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.89%1,607,000</t>
+          <t>0.84%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1607000</v>
+        <v>1032000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.6%422.5</t>
+          <t>-9.9%259.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>422.5</v>
+        <v>259.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.84%1,032,000</t>
+          <t>0.83%1,607,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1032000</v>
+        <v>1607000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.8%823</t>
+          <t>-0.73%817</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.72%455,000</t>
+          <t>0.74%455,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-9.28%2395</t>
+          <t>-2.71%2330</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.28%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2395</v>
+        <v>2330</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.57%125.5</t>
+          <t>-2.39%122.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.57%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>125.5</v>
+        <v>122.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.96%492</t>
+          <t>+1.63%500</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>+1.63%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.29%305,000</t>
+          <t>0.30%305,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0%66.7</t>
+          <t>+2.7%68.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>66.7</v>
+        <v>68.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.29%2,213,556</t>
+          <t>0.30%2,213,556</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:56</t>
+          <t>2026-09-03 21:25:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.33%272</t>
+          <t>-3.31%263</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.99%249</t>
+          <t>-3.01%241.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>249</v>
+        <v>241.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.6%50.6</t>
+          <t>-2.77%49.2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>50.6</v>
+        <v>49.2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>6640均華</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.07%1185</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1305</v>
+        <v>1185</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.11%42,000</t>
+          <t>0.24%103,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>42000</v>
+        <v>103000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,34 +3432,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6640均華</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+8.04%1210</t>
+          <t>+3.45%1350</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+8.04%</t>
+          <t>+3.45%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1210</v>
+        <v>1350</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.03%13,000</t>
+          <t>0.11%42,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>13000</v>
+        <v>42000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.74%47.2</t>
+          <t>+3.28%48.75</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>47.2</v>
+        <v>48.75</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3615,25 +3615,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>4441振大環球</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-0.87%171.5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1200</v>
+        <v>171.5</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%4,000</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3676,25 +3676,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4441振大環球</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+0.29%173</t>
+          <t>-2.56%722</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>173</v>
+        <v>722</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>&lt;0.01%4,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>4000</v>
+        <v>660</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-2.63%741</t>
+          <t>-6.56%470</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-6.56%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>741</v>
+        <v>470</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,21 +3798,21 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2886兆豐金</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-4.37%503</t>
+          <t>+2.86%50.4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>+2.86%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>503</v>
+        <v>50.4</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:57</t>
+          <t>2026-09-03 21:25:19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-1.03%143.5</t>
+          <t>+2.44%147</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>143.5</v>
+        <v>147</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3894,67 +3894,6 @@
         </is>
       </c>
       <c r="M57" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-03 01:12:57</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2886兆豐金</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>+1.03%49</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>+1.03%</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>49</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:15</t>
+          <t>2026-09-03 21:39:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:16</t>
+          <t>2026-09-03 21:39:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:18</t>
+          <t>2026-09-03 21:40:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:19</t>
+          <t>2026-09-03 21:40:01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:57</t>
+          <t>2026-09-03 21:55:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:59</t>
+          <t>2026-09-03 21:55:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:00</t>
+          <t>2026-09-03 21:55:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:01</t>
+          <t>2026-09-03 21:55:55</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:52</t>
+          <t>2026-09-03 22:31:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:53</t>
+          <t>2026-09-03 22:31:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:54</t>
+          <t>2026-09-03 22:31:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:55</t>
+          <t>2026-09-03 22:31:18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:14</t>
+          <t>2026-09-03 22:44:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:16</t>
+          <t>2026-09-03 22:44:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:17</t>
+          <t>2026-09-03 22:44:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:18</t>
+          <t>2026-09-03 22:44:34</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:30</t>
+          <t>2026-09-03 23:00:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:32</t>
+          <t>2026-09-03 23:00:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:33</t>
+          <t>2026-09-03 23:00:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:34</t>
+          <t>2026-09-03 23:00:24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
